--- a/artfynd/A 30892-2026 artfynd.xlsx
+++ b/artfynd/A 30892-2026 artfynd.xlsx
@@ -3079,7 +3079,7 @@
         <v>135905243</v>
       </c>
       <c r="B25" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 30892-2026 artfynd.xlsx
+++ b/artfynd/A 30892-2026 artfynd.xlsx
@@ -3079,7 +3079,7 @@
         <v>135905243</v>
       </c>
       <c r="B25" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 30892-2026 artfynd.xlsx
+++ b/artfynd/A 30892-2026 artfynd.xlsx
@@ -3079,7 +3079,7 @@
         <v>135905243</v>
       </c>
       <c r="B25" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -5729,7 +5729,7 @@
         <v>136573239</v>
       </c>
       <c r="B50" t="n">
-        <v>57193</v>
+        <v>57195</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
